--- a/Assets/Data/Excel/DropTable.xlsx
+++ b/Assets/Data/Excel/DropTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Desktop\Work\UnityProject\MadHatter\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B6BA37-E628-482B-A5D6-B4ABAF34B62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A47F686-498F-4BA3-BAE2-A63F77FADDF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="28800" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="180" windowWidth="28800" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DropTable" sheetId="1" r:id="rId1"/>
@@ -457,7 +457,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -468,7 +468,7 @@
         <v>8</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">

--- a/Assets/Data/Excel/DropTable.xlsx
+++ b/Assets/Data/Excel/DropTable.xlsx
@@ -15,12 +15,12 @@
   <sheets>
     <sheet name="DropTable" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>uniqueId</t>
   </si>
@@ -34,27 +34,60 @@
     <t>weight</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>E_001</t>
+  </si>
+  <si>
     <t>potion_hp_small</t>
   </si>
   <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>potion_hp_medium</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>goblin_01</t>
   </si>
   <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>potion_hp_large</t>
   </si>
   <si>
-    <t>E_001</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>6</t>
+  </si>
+  <si>
+    <t>65</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -62,32 +95,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -103,10 +117,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -411,14 +423,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -432,86 +438,93 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <v>65</v>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>